--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Mistral-Small-3.2-24B-Instruct-2506/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Mistral-Small-3.2-24B-Instruct-2506/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
+        <v>50</v>
+      </c>
+      <c r="D2">
+        <v>315</v>
+      </c>
+      <c r="E2">
+        <v>15</v>
+      </c>
+      <c r="G2">
         <v>46</v>
-      </c>
-      <c r="D2">
-        <v>312</v>
-      </c>
-      <c r="E2">
-        <v>20</v>
-      </c>
-      <c r="G2">
-        <v>48</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="D3">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="H3">
         <v>426</v>
